--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
   <si>
     <t>Filename</t>
   </si>
@@ -808,679 +808,685 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9796,0.0019,0.0050,0.0018</t>
-  </si>
-  <si>
-    <t>0.0015,0.0083,0.0000,0.9983</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.1392,0.0015,0.0001,0.9448</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9918,0.0012,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0019,0.0000,0.9986</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.6034,0.0008,0.0000,0.5149</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.6713,0.0032,0.3395,0.0003</t>
+  </si>
+  <si>
+    <t>0.0181,0.0009,0.9837,0.0002</t>
+  </si>
+  <si>
+    <t>0.9044,0.0003,0.1220,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9942,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0002,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.6427,0.0007,0.4369,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9164,0.0549,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9725,0.0028,0.0151,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.9885,0.0565,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0009,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0012,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9683,0.0310,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.9747,0.1757,0.0001</t>
+  </si>
+  <si>
+    <t>0.0184,0.1384,0.3192,0.0090</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.9978,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0034,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9960,0.0039,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0059,0.0490,0.0225,0.9609</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.1823,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0740,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0004,0.9977,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0049,0.0028,0.9897,0.0014</t>
+  </si>
+  <si>
+    <t>0.9981,0.0015,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0026,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0035,0.9941,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9914,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.9922,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9880,0.0002,0.0102,0.0001</t>
+  </si>
+  <si>
+    <t>0.0338,0.0021,0.9650,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9781,0.9835,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.4789,0.9834,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0335,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9973,0.9486,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0031,0.9995</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0008,0.9999</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.7416,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9869,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.8529,0.7374,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9505,0.9924,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9652,0.6255,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0001</t>
   </si>
   <si>
+    <t>0.9995,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0005,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9984,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9968,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8106,0.2562,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.7015,0.0005,0.3331,0.0003</t>
+  </si>
+  <si>
+    <t>0.7025,0.0025,0.2080,0.0014</t>
+  </si>
+  <si>
+    <t>0.9565,0.0034,0.0109,0.0019</t>
+  </si>
+  <si>
+    <t>0.8650,0.0022,0.0783,0.0040</t>
+  </si>
+  <si>
+    <t>0.0009,0.0031,0.0073,0.9830</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9891,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9980,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9146,0.0698,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9491,0.0388,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8979,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.2638,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0315,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0366,0.0004,0.9719,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9635,0.0007,0.0259,0.0004</t>
+  </si>
+  <si>
+    <t>0.0232,0.0000,0.9894,0.0000</t>
+  </si>
+  <si>
+    <t>0.8470,0.0051,0.1128,0.0022</t>
+  </si>
+  <si>
+    <t>0.0124,0.0007,0.0009,0.9951</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.9884,0.3401,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.9900,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.1991,0.8012,0.0062,0.0040</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0881,0.0001,0.0001,0.9713</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.2793,0.0001,0.1079,0.1532</t>
+  </si>
+  <si>
+    <t>0.9961,0.0009,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.0674,0.9238,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9569,0.0169,0.0061,0.0008</t>
+  </si>
+  <si>
+    <t>0.9848,0.0030,0.0042,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0007,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0018,0.0024,0.0020</t>
+  </si>
+  <si>
+    <t>0.8755,0.0904,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9311,0.0651,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.8129,0.2168,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9131,0.0345,0.0270,0.0031</t>
+  </si>
+  <si>
+    <t>0.9953,0.0044,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0144,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0024,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9760,0.0042,0.0105,0.0010</t>
+  </si>
+  <si>
+    <t>0.0009,0.0072,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0059,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0010,0.9972,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.0004,0.9944,0.0004</t>
+  </si>
+  <si>
+    <t>0.6250,0.0010,0.4681,0.0001</t>
+  </si>
+  <si>
+    <t>0.7953,0.0007,0.2396,0.0001</t>
+  </si>
+  <si>
+    <t>0.0095,0.0042,0.9848,0.0002</t>
+  </si>
+  <si>
+    <t>0.9807,0.0015,0.0083,0.0002</t>
+  </si>
+  <si>
+    <t>0.9840,0.0008,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.0310,0.0019,0.9780,0.0000</t>
+  </si>
+  <si>
+    <t>0.0184,0.9865,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.9981,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4810,0.6565,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9795,0.0134,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.1263,0.8781,0.0036,0.0011</t>
+  </si>
+  <si>
+    <t>0.9920,0.0006,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9393,0.0031,0.0231,0.0019</t>
+  </si>
+  <si>
+    <t>0.4681,0.0050,0.5515,0.0006</t>
+  </si>
+  <si>
+    <t>0.3867,0.0013,0.6241,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.0002,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0012,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0047,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0135,0.0051,0.9802,0.0009</t>
+  </si>
+  <si>
+    <t>0.9427,0.0018,0.0247,0.0026</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0092,0.0014,0.9886,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0009,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.0017,0.9959,0.0007</t>
+  </si>
+  <si>
+    <t>0.9856,0.0005,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.9643,0.0000,0.0425,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9615,0.0009,0.0375,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0003,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.2858,0.0006,0.7934,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9975,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9925,0.0001,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.0382,0.0002,0.9680,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0143,0.0001,0.9856,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.3016,0.7090,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0986,0.0265,0.7642,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.4055,0.7881,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9564,0.0022,0.0240,0.0007</t>
-  </si>
-  <si>
-    <t>0.9417,0.0646,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.9945,0.0085,0.0000</t>
-  </si>
-  <si>
-    <t>0.0110,0.5774,0.1459,0.0027</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0014,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0114,0.0000,0.9755,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0117,0.1915,0.0470,0.6799</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.2900,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0026,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0473,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0010,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0026,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0008,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9409,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0040,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9973,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9935,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0142,0.9874,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0002,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.2316,0.0037,0.7095,0.0024</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9791,0.9475,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.2978,0.9776,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.1575,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9480,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0191,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0014,0.9998</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9748,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9362,0.9936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9723,0.8829,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.7938,0.8687,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9812,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9650,0.9778,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0096,0.0020,0.9897,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9984,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9361,0.0582,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.6891,0.0092,0.1688,0.0017</t>
-  </si>
-  <si>
-    <t>0.9747,0.0005,0.0169,0.0002</t>
-  </si>
-  <si>
-    <t>0.9753,0.0041,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.1060,0.0061,0.8633,0.0030</t>
-  </si>
-  <si>
-    <t>0.0002,0.0102,0.0002,0.9984</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9915,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.5311,0.5174,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9785,0.0179,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0005,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.7754,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.1779,0.9920,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0076,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0477,0.0001,0.9757,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0000,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.6209,0.0006,0.3134,0.0019</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.8218,0.0005,0.1819,0.0005</t>
-  </si>
-  <si>
-    <t>0.0183,0.0001,0.0002,0.9935</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0004,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.7319,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9963,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.1198,0.8962,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.0112,0.0001,0.0003,0.9927</t>
-  </si>
-  <si>
-    <t>0.0016,0.0063,0.9931,0.0126</t>
-  </si>
-  <si>
-    <t>0.9825,0.0001,0.0015,0.0062</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.4163,0.6064,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0898,0.0815,0.6696,0.0014</t>
-  </si>
-  <si>
-    <t>0.9928,0.0009,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.4777,0.4157,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9757,0.0111,0.0011,0.0016</t>
-  </si>
-  <si>
-    <t>0.9845,0.0115,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.8856,0.1054,0.0047,0.0010</t>
-  </si>
-  <si>
-    <t>0.9891,0.0104,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9950,0.0008,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9987,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9844,0.0112,0.0025,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0028,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0034,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0107,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.0249,0.9768,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0006,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0011,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.6030,0.0023,0.3210,0.0012</t>
-  </si>
-  <si>
-    <t>0.0081,0.0072,0.9769,0.0006</t>
-  </si>
-  <si>
-    <t>0.0070,0.0443,0.9607,0.0005</t>
-  </si>
-  <si>
-    <t>0.9064,0.0021,0.0960,0.0002</t>
-  </si>
-  <si>
-    <t>0.2252,0.0041,0.7687,0.0018</t>
-  </si>
-  <si>
-    <t>0.0406,0.0004,0.9741,0.0001</t>
-  </si>
-  <si>
-    <t>0.4066,0.7496,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.9964,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6644,0.4452,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9397,0.0649,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0892,0.9184,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.8938,0.0164,0.0188,0.0014</t>
-  </si>
-  <si>
-    <t>0.9974,0.0000,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9226,0.0037,0.0357,0.0030</t>
-  </si>
-  <si>
-    <t>0.9528,0.0012,0.0317,0.0008</t>
-  </si>
-  <si>
-    <t>0.9396,0.0012,0.0283,0.0019</t>
-  </si>
-  <si>
-    <t>0.0239,0.0250,0.8415,0.0035</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0067,0.9956,0.0005</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9535,0.0426,0.0029,0.0017</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9709,0.0024,0.0177,0.0009</t>
-  </si>
-  <si>
-    <t>0.9965,0.0011,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.4451,0.0009,0.5589,0.0006</t>
-  </si>
-  <si>
-    <t>0.9501,0.0005,0.0207,0.0033</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.3463,0.9875,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0116,0.0001,0.9912,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0016,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0014,0.9972,0.0007</t>
-  </si>
-  <si>
-    <t>0.9868,0.0002,0.0087,0.0001</t>
-  </si>
-  <si>
-    <t>0.8056,0.0000,0.2464,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0025,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0404,0.0019,0.9735,0.0006</t>
-  </si>
-  <si>
-    <t>0.0025,0.0100,0.9947,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0061,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0003,0.9974,0.0003</t>
-  </si>
-  <si>
-    <t>0.5850,0.0007,0.4063,0.0021</t>
-  </si>
-  <si>
-    <t>0.0027,0.0005,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0002,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0113,0.0001,0.0007,0.9959</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9294,0.0034,0.0246,0.0121</t>
+    <t>0.9990,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0010,0.9956,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0027,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0006,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0006,0.9889,0.0068</t>
+  </si>
+  <si>
+    <t>0.0028,0.0004,0.9959,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.0000,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.9543,0.0013,0.0014,0.0384</t>
+  </si>
+  <si>
+    <t>0.0006,0.0039,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0027,0.0000,0.0007,0.9982</t>
+  </si>
+  <si>
+    <t>0.9737,0.0014,0.0106,0.0018</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1872,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1886,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1894,7 +1900,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1905,10 +1911,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1922,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1936,7 +1942,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1950,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1964,7 +1970,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1978,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1992,7 +1998,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2006,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2020,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2034,7 +2040,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2048,7 +2054,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2059,10 +2065,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2076,7 +2082,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2090,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2104,7 +2110,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2118,7 +2124,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2132,7 +2138,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2146,7 +2152,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2160,7 +2166,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2174,7 +2180,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,10 +2191,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2202,7 +2208,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,7 +2236,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2244,7 +2250,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2258,7 +2264,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,10 +2275,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,10 +2289,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2300,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2311,10 +2317,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2328,7 +2334,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2342,7 +2348,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2356,7 +2362,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2370,7 +2376,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2381,10 +2387,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2398,7 +2404,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2412,7 +2418,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2426,7 +2432,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2440,7 +2446,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2454,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2468,7 +2474,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,7 +2488,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2496,7 +2502,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2510,7 +2516,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2524,7 +2530,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2538,7 +2544,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2552,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2566,7 +2572,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2580,7 +2586,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2594,7 +2600,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2608,7 +2614,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2622,7 +2628,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2636,7 +2642,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2650,7 +2656,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2664,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2678,7 +2684,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2692,7 +2698,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2706,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2720,7 +2726,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2734,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2748,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2762,7 +2768,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2776,7 +2782,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2790,7 +2796,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2804,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,7 +2824,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2832,7 +2838,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2846,7 +2852,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2860,7 +2866,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2874,7 +2880,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2888,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2902,7 +2908,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2916,7 +2922,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2930,7 +2936,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2944,7 +2950,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2958,7 +2964,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2972,7 +2978,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3000,7 +3006,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3014,7 +3020,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,7 +3034,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,7 +3048,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3056,7 +3062,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3070,7 +3076,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3084,7 +3090,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3098,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3112,7 +3118,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3126,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3140,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3154,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>272</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3168,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3182,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3196,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3210,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3224,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3238,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3252,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3266,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3280,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3294,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3308,7 +3314,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3322,7 +3328,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3336,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3350,7 +3356,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3364,7 +3370,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3378,7 +3384,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3392,7 +3398,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3406,7 +3412,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3420,7 +3426,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3434,7 +3440,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>285</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3448,7 +3454,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3462,7 +3468,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3476,7 +3482,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,7 +3496,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,10 +3507,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3518,7 +3524,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3532,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3546,7 +3552,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3560,7 +3566,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3574,7 +3580,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3588,7 +3594,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3599,10 +3605,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,7 +3622,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3630,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>377</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3644,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>268</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3658,7 +3664,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3672,7 +3678,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3686,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3700,7 +3706,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3714,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>268</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3728,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,7 +3748,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3756,7 +3762,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3770,7 +3776,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3784,7 +3790,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3798,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3812,7 +3818,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3826,7 +3832,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3840,7 +3846,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3854,7 +3860,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3868,7 +3874,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3882,7 +3888,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3896,7 +3902,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3907,10 +3913,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3924,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3938,7 +3944,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3952,7 +3958,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3966,7 +3972,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3980,7 +3986,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>316</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3994,7 +4000,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4008,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>397</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4022,7 +4028,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4033,10 +4039,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4064,7 +4070,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4078,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4092,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4103,10 +4109,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4120,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4148,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4162,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4176,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4190,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4204,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>316</v>
+        <v>413</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4218,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4232,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>272</v>
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4246,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4260,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4274,7 +4280,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4288,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4302,7 +4308,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4316,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4330,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4344,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4358,7 +4364,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4372,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4386,7 +4392,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4400,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4414,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4428,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4442,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4456,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4470,7 +4476,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>286</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4484,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4498,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4512,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4526,7 +4532,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4537,10 +4543,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4568,7 +4574,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4579,10 +4585,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4596,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4610,7 +4616,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4624,7 +4630,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4635,10 +4641,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4652,7 +4658,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4666,7 +4672,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4680,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4694,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4708,7 +4714,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,10 +4725,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,10 +4739,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4750,7 +4756,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>299</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4764,7 +4770,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4778,7 +4784,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4792,7 +4798,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4806,7 +4812,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4820,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4834,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4848,7 +4854,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4862,7 +4868,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4876,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4890,7 +4896,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4904,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4918,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4932,7 +4938,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4946,7 +4952,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4960,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4974,7 +4980,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4988,7 +4994,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5002,7 +5008,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5016,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>463</v>
+        <v>328</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5030,7 +5036,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5044,7 +5050,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>286</v>
+        <v>328</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5058,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5072,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5086,7 +5092,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5100,7 +5106,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5114,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5128,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5142,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5156,7 +5162,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5170,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5184,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>473</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5212,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5226,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5240,7 +5246,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5254,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5268,7 +5274,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5282,7 +5288,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5296,7 +5302,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,10 +5313,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5324,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5338,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,7 +5358,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5366,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5380,7 +5386,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5394,7 +5400,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>487</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5408,7 +5414,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5422,7 +5428,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
